--- a/src/main/resources/espacios/Software/0 - Questions OOP.xlsx
+++ b/src/main/resources/espacios/Software/0 - Questions OOP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="535">
   <si>
     <t xml:space="preserve">What is Object-Oriented Programming (OOP)?</t>
   </si>
@@ -1116,23 +1116,7 @@
     <t xml:space="preserve">ðə Liskov ˌsʌbstɪˈtuʃən ˈprɪnsəpəl</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(LSP) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">states that subtypes must be substitutable for their base types without altering the correctness of the program.</t>
-    </r>
+    <t xml:space="preserve">(LSP) states that subtypes must be substitutable for their base types without altering the correctness of the program.</t>
   </si>
   <si>
     <t xml:space="preserve">(LSP) establece que los subtipos deben ser sustituibles por sus tipos base sin alterar la corrección del programa.</t>
@@ -1652,7 +1636,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1673,11 +1657,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1737,11 +1716,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1768,9 +1747,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>101520</xdr:colOff>
+      <xdr:colOff>100800</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>3286080</xdr:rowOff>
+      <xdr:rowOff>3285360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1783,8 +1762,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="812880"/>
-          <a:ext cx="5791320" cy="3286080"/>
+          <a:off x="29378160" y="812880"/>
+          <a:ext cx="5790600" cy="3285360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1806,9 +1785,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>101520</xdr:colOff>
+      <xdr:colOff>100800</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>3467160</xdr:rowOff>
+      <xdr:rowOff>3466440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1821,8 +1800,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="6012720"/>
-          <a:ext cx="5791320" cy="3467160"/>
+          <a:off x="29378160" y="6012720"/>
+          <a:ext cx="5790600" cy="3466440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1844,9 +1823,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>196920</xdr:colOff>
+      <xdr:colOff>196200</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1676160</xdr:rowOff>
+      <xdr:rowOff>1675440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1859,8 +1838,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="9982800"/>
-          <a:ext cx="5886720" cy="1676160"/>
+          <a:off x="29378160" y="9982800"/>
+          <a:ext cx="5886000" cy="1675440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1882,9 +1861,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>92160</xdr:colOff>
+      <xdr:colOff>91440</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>1228320</xdr:rowOff>
+      <xdr:rowOff>1227600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1897,8 +1876,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="11982600"/>
-          <a:ext cx="5781960" cy="1228320"/>
+          <a:off x="29378160" y="11982600"/>
+          <a:ext cx="5781240" cy="1227600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1920,9 +1899,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>800280</xdr:colOff>
+      <xdr:colOff>799560</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>1380600</xdr:rowOff>
+      <xdr:rowOff>1379880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1935,8 +1914,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="13559040"/>
-          <a:ext cx="3238560" cy="1380600"/>
+          <a:off x="29378160" y="13559040"/>
+          <a:ext cx="3238200" cy="1379880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1958,9 +1937,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>444600</xdr:colOff>
+      <xdr:colOff>443880</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>3019320</xdr:rowOff>
+      <xdr:rowOff>3018600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1973,8 +1952,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="15635520"/>
-          <a:ext cx="3695760" cy="3019320"/>
+          <a:off x="29378160" y="15635520"/>
+          <a:ext cx="3695040" cy="3018600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1996,9 +1975,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>216000</xdr:colOff>
+      <xdr:colOff>215280</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>2180880</xdr:rowOff>
+      <xdr:rowOff>2180160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2011,8 +1990,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="19578960"/>
-          <a:ext cx="3467160" cy="2180880"/>
+          <a:off x="29378160" y="19578960"/>
+          <a:ext cx="3466440" cy="2180160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2034,9 +2013,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>365040</xdr:colOff>
+      <xdr:colOff>364320</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>1514160</xdr:rowOff>
+      <xdr:rowOff>1513440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2049,8 +2028,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="22397040"/>
-          <a:ext cx="4429080" cy="1514160"/>
+          <a:off x="29378160" y="22397040"/>
+          <a:ext cx="4428360" cy="1513440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2072,9 +2051,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>568440</xdr:colOff>
+      <xdr:colOff>567720</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>4133880</xdr:rowOff>
+      <xdr:rowOff>4133160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2087,8 +2066,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="24738480"/>
-          <a:ext cx="3819600" cy="4133880"/>
+          <a:off x="29378160" y="24738480"/>
+          <a:ext cx="3818880" cy="4133160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2110,9 +2089,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>282600</xdr:colOff>
+      <xdr:colOff>281880</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>3905280</xdr:rowOff>
+      <xdr:rowOff>3904560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2125,8 +2104,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="29230920"/>
-          <a:ext cx="3533760" cy="3905280"/>
+          <a:off x="29378160" y="29230920"/>
+          <a:ext cx="3533040" cy="3904560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2148,9 +2127,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>95400</xdr:colOff>
+      <xdr:colOff>94680</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>3819600</xdr:rowOff>
+      <xdr:rowOff>3818880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2163,8 +2142,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="29378880" y="33476040"/>
-          <a:ext cx="4972320" cy="3819600"/>
+          <a:off x="29378160" y="33476040"/>
+          <a:ext cx="4971600" cy="3818880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2191,9 +2170,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>403200</xdr:colOff>
+      <xdr:colOff>402480</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2695320</xdr:rowOff>
+      <xdr:rowOff>2694600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2206,8 +2185,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="0"/>
-          <a:ext cx="4467240" cy="2695320"/>
+          <a:off x="26016120" y="0"/>
+          <a:ext cx="4466160" cy="2694600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2229,9 +2208,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>669960</xdr:colOff>
+      <xdr:colOff>669240</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>3228840</xdr:rowOff>
+      <xdr:rowOff>3228120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2244,8 +2223,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="5369040"/>
-          <a:ext cx="4734000" cy="3228840"/>
+          <a:off x="26016120" y="5369040"/>
+          <a:ext cx="4732920" cy="3228120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2267,9 +2246,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>711360</xdr:colOff>
+      <xdr:colOff>710640</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>4162320</xdr:rowOff>
+      <xdr:rowOff>4161600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2282,8 +2261,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="9061920"/>
-          <a:ext cx="3962520" cy="4162320"/>
+          <a:off x="26016120" y="9061920"/>
+          <a:ext cx="3961800" cy="4161600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2305,9 +2284,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>803520</xdr:colOff>
+      <xdr:colOff>802800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>5334120</xdr:rowOff>
+      <xdr:rowOff>5333400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2320,8 +2299,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="14204880"/>
-          <a:ext cx="4867560" cy="5334120"/>
+          <a:off x="26016120" y="14204880"/>
+          <a:ext cx="4866480" cy="5333400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2343,9 +2322,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>412920</xdr:colOff>
+      <xdr:colOff>412200</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>4048200</xdr:rowOff>
+      <xdr:rowOff>4047480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2358,8 +2337,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="20070360"/>
-          <a:ext cx="4476960" cy="4048200"/>
+          <a:off x="26016120" y="20070360"/>
+          <a:ext cx="4475880" cy="4047480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2381,9 +2360,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>685800</xdr:colOff>
+      <xdr:colOff>685080</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>3000240</xdr:rowOff>
+      <xdr:rowOff>2999520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2396,8 +2375,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="26072640"/>
-          <a:ext cx="5562720" cy="3000240"/>
+          <a:off x="26016120" y="26072640"/>
+          <a:ext cx="5561640" cy="2999520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2419,9 +2398,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>469800</xdr:colOff>
+      <xdr:colOff>469080</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>3247920</xdr:rowOff>
+      <xdr:rowOff>3247200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2434,8 +2413,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="30461760"/>
-          <a:ext cx="4533840" cy="3247920"/>
+          <a:off x="26016120" y="30461760"/>
+          <a:ext cx="4532760" cy="3247200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2457,9 +2436,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>130320</xdr:colOff>
+      <xdr:colOff>129600</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>3152520</xdr:rowOff>
+      <xdr:rowOff>3151800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2472,8 +2451,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="26014680" y="34050600"/>
-          <a:ext cx="3381480" cy="3152520"/>
+          <a:off x="26016120" y="34050600"/>
+          <a:ext cx="3380760" cy="3151800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2500,9 +2479,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>285840</xdr:colOff>
+      <xdr:colOff>285120</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>2009520</xdr:rowOff>
+      <xdr:rowOff>2008800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2515,8 +2494,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="1137960"/>
-          <a:ext cx="5162760" cy="2009520"/>
+          <a:off x="28354680" y="1137960"/>
+          <a:ext cx="5162040" cy="2008800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2538,9 +2517,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>104760</xdr:colOff>
+      <xdr:colOff>104040</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1190160</xdr:rowOff>
+      <xdr:rowOff>1189440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2553,8 +2532,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="3531240"/>
-          <a:ext cx="4981680" cy="1190160"/>
+          <a:off x="28354680" y="3531240"/>
+          <a:ext cx="4980960" cy="1189440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2576,9 +2555,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>523800</xdr:colOff>
+      <xdr:colOff>523080</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2276280</xdr:rowOff>
+      <xdr:rowOff>2275560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2591,8 +2570,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="5625000"/>
-          <a:ext cx="5400720" cy="2276280"/>
+          <a:off x="28354680" y="5625000"/>
+          <a:ext cx="5400000" cy="2275560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2614,9 +2593,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>730080</xdr:colOff>
+      <xdr:colOff>729360</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>1723680</xdr:rowOff>
+      <xdr:rowOff>1722960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2629,8 +2608,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="8088480"/>
-          <a:ext cx="3981600" cy="1723680"/>
+          <a:off x="28354680" y="8088480"/>
+          <a:ext cx="3980520" cy="1722960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2652,9 +2631,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>165240</xdr:colOff>
+      <xdr:colOff>164520</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1714320</xdr:rowOff>
+      <xdr:rowOff>1713600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2667,8 +2646,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="10619640"/>
-          <a:ext cx="4229280" cy="1714320"/>
+          <a:off x="28354680" y="10619640"/>
+          <a:ext cx="4228560" cy="1713600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2690,9 +2669,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>19080</xdr:colOff>
+      <xdr:colOff>18360</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>3333600</xdr:rowOff>
+      <xdr:rowOff>3332880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2705,8 +2684,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="12706200"/>
-          <a:ext cx="4896000" cy="3333600"/>
+          <a:off x="28354680" y="12706200"/>
+          <a:ext cx="4895280" cy="3332880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2728,9 +2707,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>146160</xdr:colOff>
+      <xdr:colOff>145440</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>1952280</xdr:rowOff>
+      <xdr:rowOff>1951560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2743,8 +2722,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="17653680"/>
-          <a:ext cx="4210200" cy="1952280"/>
+          <a:off x="28354680" y="17653680"/>
+          <a:ext cx="4209480" cy="1951560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2766,9 +2745,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>352440</xdr:colOff>
+      <xdr:colOff>351720</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>1638000</xdr:rowOff>
+      <xdr:rowOff>1637280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2781,8 +2760,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="19988640"/>
-          <a:ext cx="5229360" cy="1638000"/>
+          <a:off x="28354680" y="19988640"/>
+          <a:ext cx="5228640" cy="1637280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2804,9 +2783,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>780840</xdr:colOff>
+      <xdr:colOff>780120</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>1504800</xdr:rowOff>
+      <xdr:rowOff>1504080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2819,8 +2798,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="22444200"/>
-          <a:ext cx="3219480" cy="1504800"/>
+          <a:off x="28354680" y="22444200"/>
+          <a:ext cx="3218400" cy="1504080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2842,9 +2821,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>108000</xdr:colOff>
+      <xdr:colOff>107280</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>2095200</xdr:rowOff>
+      <xdr:rowOff>2094480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2857,8 +2836,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="24445440"/>
-          <a:ext cx="4172040" cy="2095200"/>
+          <a:off x="28354680" y="24445440"/>
+          <a:ext cx="4171320" cy="2094480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2880,9 +2859,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>22320</xdr:colOff>
+      <xdr:colOff>21600</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>2647800</xdr:rowOff>
+      <xdr:rowOff>2647080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2895,8 +2874,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="27370440"/>
-          <a:ext cx="4086360" cy="2647800"/>
+          <a:off x="28354680" y="27370440"/>
+          <a:ext cx="4085640" cy="2647080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2918,9 +2897,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>308160</xdr:colOff>
+      <xdr:colOff>307440</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>1761840</xdr:rowOff>
+      <xdr:rowOff>1761120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2933,8 +2912,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="30465360"/>
-          <a:ext cx="4372200" cy="1761840"/>
+          <a:off x="28354680" y="30465360"/>
+          <a:ext cx="4371480" cy="1761120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2956,9 +2935,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>488880</xdr:colOff>
+      <xdr:colOff>488160</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>2933640</xdr:rowOff>
+      <xdr:rowOff>2932920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2971,8 +2950,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="28353240" y="32654160"/>
-          <a:ext cx="4552920" cy="2933640"/>
+          <a:off x="28354680" y="32654160"/>
+          <a:ext cx="4552200" cy="2932920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3100,10 +3079,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="113.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="129.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="129.48"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="116.43"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
@@ -3186,6 +3165,9 @@
       <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
@@ -3348,6 +3330,9 @@
       <c r="D18" s="1" t="s">
         <v>54</v>
       </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -3387,6 +3372,9 @@
       <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -3412,6 +3400,9 @@
       <c r="D23" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
@@ -3437,6 +3428,9 @@
       <c r="D25" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -3543,6 +3537,9 @@
       <c r="D33" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
@@ -3582,6 +3579,9 @@
       <c r="D36" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="F36" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
@@ -3649,6 +3649,9 @@
       <c r="D41" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="F41" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
@@ -3674,6 +3677,9 @@
       <c r="D43" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="F43" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
@@ -3698,6 +3704,9 @@
       </c>
       <c r="D45" s="1" t="s">
         <v>135</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3799,919 +3808,952 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F68"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="96.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="110.02"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="105.09"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="96.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="110.02"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="105.09"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="230.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>177</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="265.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>204</v>
       </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="340.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>213</v>
       </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="436.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="331.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>240</v>
       </c>
+      <c r="F29" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>249</v>
       </c>
+      <c r="F32" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="F35" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="256" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>288</v>
       </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="269.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>300</v>
       </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="264.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>306</v>
       </c>
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="1" t="s">
         <v>324</v>
       </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D60" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D61" s="1" t="s">
         <v>336</v>
       </c>
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D62" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D63" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D64" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="F64" s="2" t="s">
+      <c r="F64" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D65" s="1" t="s">
         <v>348</v>
       </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D66" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D67" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="F67" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D68" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F68" s="2" t="s">
+      <c r="F68" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4733,37 +4775,37 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F59"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="102.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="115.37"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="126.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="102.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="115.37"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="126.51"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4771,752 +4813,788 @@
       <c r="A3" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="175.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>381</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="113.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>387</v>
       </c>
+      <c r="F10" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="194" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>402</v>
       </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="148.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>405</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="151.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="274.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>426</v>
       </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F24" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>432</v>
       </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="1" t="s">
         <v>443</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="171.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>456</v>
       </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F34" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="154.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="D37" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="F37" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F38" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="132" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="1" t="s">
         <v>474</v>
       </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F40" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="179.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D42" s="1" t="s">
         <v>483</v>
       </c>
+      <c r="F42" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D43" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D45" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="218.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" s="1" t="s">
         <v>498</v>
       </c>
+      <c r="F47" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F48" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D49" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="159.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" s="1" t="s">
         <v>507</v>
       </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="1" t="s">
         <v>509</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="245.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" s="1" t="s">
         <v>513</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>515</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D54" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D55" s="1" t="s">
         <v>522</v>
       </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D56" s="1" t="s">
         <v>525</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/src/main/resources/espacios/Software/0 - Questions OOP.xlsx
+++ b/src/main/resources/espacios/Software/0 - Questions OOP.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" state="visible" r:id="rId3"/>
@@ -1636,7 +1636,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1658,19 +1658,20 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF000000"/>
-        <bgColor rgb="FF003300"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1707,20 +1708,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1747,9 +1740,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>100800</xdr:colOff>
+      <xdr:colOff>100440</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>3285360</xdr:rowOff>
+      <xdr:rowOff>3285000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1763,7 +1756,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="812880"/>
-          <a:ext cx="5790600" cy="3285360"/>
+          <a:ext cx="5790240" cy="3285000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1785,9 +1778,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>100800</xdr:colOff>
+      <xdr:colOff>100440</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>3466440</xdr:rowOff>
+      <xdr:rowOff>3466080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1801,7 +1794,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="6012720"/>
-          <a:ext cx="5790600" cy="3466440"/>
+          <a:ext cx="5790240" cy="3466080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1823,9 +1816,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>196200</xdr:colOff>
+      <xdr:colOff>195840</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1675440</xdr:rowOff>
+      <xdr:rowOff>1675080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1839,7 +1832,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="9982800"/>
-          <a:ext cx="5886000" cy="1675440"/>
+          <a:ext cx="5885640" cy="1675080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1861,9 +1854,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
+      <xdr:colOff>91080</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>1227600</xdr:rowOff>
+      <xdr:rowOff>1227240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1877,7 +1870,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="11982600"/>
-          <a:ext cx="5781240" cy="1227600"/>
+          <a:ext cx="5780880" cy="1227240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1899,9 +1892,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>799560</xdr:colOff>
+      <xdr:colOff>799200</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>1379880</xdr:rowOff>
+      <xdr:rowOff>1379520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1915,7 +1908,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="13559040"/>
-          <a:ext cx="3238200" cy="1379880"/>
+          <a:ext cx="3237840" cy="1379520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1937,9 +1930,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>443880</xdr:colOff>
+      <xdr:colOff>443520</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>3018600</xdr:rowOff>
+      <xdr:rowOff>3018240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1953,7 +1946,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="15635520"/>
-          <a:ext cx="3695040" cy="3018600"/>
+          <a:ext cx="3694680" cy="3018240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1975,9 +1968,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>215280</xdr:colOff>
+      <xdr:colOff>214920</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>2180160</xdr:rowOff>
+      <xdr:rowOff>2179800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1991,7 +1984,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="19578960"/>
-          <a:ext cx="3466440" cy="2180160"/>
+          <a:ext cx="3466080" cy="2179800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2013,9 +2006,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>364320</xdr:colOff>
+      <xdr:colOff>363960</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>1513440</xdr:rowOff>
+      <xdr:rowOff>1513080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2029,7 +2022,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="22397040"/>
-          <a:ext cx="4428360" cy="1513440"/>
+          <a:ext cx="4428000" cy="1513080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2051,9 +2044,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>567720</xdr:colOff>
+      <xdr:colOff>567360</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>4133160</xdr:rowOff>
+      <xdr:rowOff>4132800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2067,7 +2060,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="24738480"/>
-          <a:ext cx="3818880" cy="4133160"/>
+          <a:ext cx="3818520" cy="4132800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2089,9 +2082,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>281880</xdr:colOff>
+      <xdr:colOff>281520</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>3904560</xdr:rowOff>
+      <xdr:rowOff>3904200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2105,7 +2098,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="29230920"/>
-          <a:ext cx="3533040" cy="3904560"/>
+          <a:ext cx="3532680" cy="3904200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2127,9 +2120,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>94680</xdr:colOff>
+      <xdr:colOff>94320</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>3818880</xdr:rowOff>
+      <xdr:rowOff>3818520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2143,7 +2136,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="29378160" y="33476040"/>
-          <a:ext cx="4971600" cy="3818880"/>
+          <a:ext cx="4971240" cy="3818520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2170,9 +2163,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>402480</xdr:colOff>
+      <xdr:colOff>402120</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>2694600</xdr:rowOff>
+      <xdr:rowOff>2694240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2186,7 +2179,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="0"/>
-          <a:ext cx="4466160" cy="2694600"/>
+          <a:ext cx="4465800" cy="2694240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2208,9 +2201,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>669240</xdr:colOff>
+      <xdr:colOff>668880</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>3228120</xdr:rowOff>
+      <xdr:rowOff>3227760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2224,7 +2217,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="5369040"/>
-          <a:ext cx="4732920" cy="3228120"/>
+          <a:ext cx="4732560" cy="3227760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2246,9 +2239,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>710640</xdr:colOff>
+      <xdr:colOff>710280</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>4161600</xdr:rowOff>
+      <xdr:rowOff>4161240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2262,7 +2255,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="9061920"/>
-          <a:ext cx="3961800" cy="4161600"/>
+          <a:ext cx="3961440" cy="4161240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2284,9 +2277,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>802800</xdr:colOff>
+      <xdr:colOff>802440</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>5333400</xdr:rowOff>
+      <xdr:rowOff>5333040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2300,7 +2293,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="14204880"/>
-          <a:ext cx="4866480" cy="5333400"/>
+          <a:ext cx="4866120" cy="5333040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2322,9 +2315,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>412200</xdr:colOff>
+      <xdr:colOff>411840</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>4047480</xdr:rowOff>
+      <xdr:rowOff>4047120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2338,7 +2331,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="20070360"/>
-          <a:ext cx="4475880" cy="4047480"/>
+          <a:ext cx="4475520" cy="4047120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2360,9 +2353,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>685080</xdr:colOff>
+      <xdr:colOff>684720</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>2999520</xdr:rowOff>
+      <xdr:rowOff>2999160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2376,7 +2369,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="26072640"/>
-          <a:ext cx="5561640" cy="2999520"/>
+          <a:ext cx="5561280" cy="2999160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2398,9 +2391,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>469080</xdr:colOff>
+      <xdr:colOff>468720</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>3247200</xdr:rowOff>
+      <xdr:rowOff>3246840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2414,7 +2407,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="30461760"/>
-          <a:ext cx="4532760" cy="3247200"/>
+          <a:ext cx="4532400" cy="3246840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2436,9 +2429,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>129600</xdr:colOff>
+      <xdr:colOff>129240</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>3151800</xdr:rowOff>
+      <xdr:rowOff>3151440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2452,7 +2445,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="26016120" y="34050600"/>
-          <a:ext cx="3380760" cy="3151800"/>
+          <a:ext cx="3380400" cy="3151440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2478,10 +2471,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>285120</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5161680</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>2008800</xdr:rowOff>
+      <xdr:rowOff>2008440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2495,7 +2488,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="1137960"/>
-          <a:ext cx="5162040" cy="2008800"/>
+          <a:ext cx="5161680" cy="2008440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2516,10 +2509,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>104040</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4980600</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1189440</xdr:rowOff>
+      <xdr:rowOff>1189080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2533,7 +2526,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="3531240"/>
-          <a:ext cx="4980960" cy="1189440"/>
+          <a:ext cx="4980600" cy="1189080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2554,10 +2547,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>523080</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5399640</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2275560</xdr:rowOff>
+      <xdr:rowOff>2275200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2571,7 +2564,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="5625000"/>
-          <a:ext cx="5400000" cy="2275560"/>
+          <a:ext cx="5399640" cy="2275200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2592,10 +2585,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>729360</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3980160</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>1722960</xdr:rowOff>
+      <xdr:rowOff>1722600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2609,7 +2602,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="8088480"/>
-          <a:ext cx="3980520" cy="1722960"/>
+          <a:ext cx="3980160" cy="1722600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2630,10 +2623,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>164520</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4228200</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>1713600</xdr:rowOff>
+      <xdr:rowOff>1713240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2647,7 +2640,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="10619640"/>
-          <a:ext cx="4228560" cy="1713600"/>
+          <a:ext cx="4228200" cy="1713240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2668,10 +2661,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>18360</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4894920</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>3332880</xdr:rowOff>
+      <xdr:rowOff>3332520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2685,7 +2678,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="12706200"/>
-          <a:ext cx="4895280" cy="3332880"/>
+          <a:ext cx="4894920" cy="3332520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2706,10 +2699,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>145440</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4209120</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>1951560</xdr:rowOff>
+      <xdr:rowOff>1951200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2723,7 +2716,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="17653680"/>
-          <a:ext cx="4209480" cy="1951560"/>
+          <a:ext cx="4209120" cy="1951200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2744,10 +2737,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>351720</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>5228280</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>1637280</xdr:rowOff>
+      <xdr:rowOff>1636920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2761,7 +2754,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="19988640"/>
-          <a:ext cx="5228640" cy="1637280"/>
+          <a:ext cx="5228280" cy="1636920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2782,10 +2775,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>780120</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>3218040</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>1504080</xdr:rowOff>
+      <xdr:rowOff>1503720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2799,7 +2792,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="22444200"/>
-          <a:ext cx="3218400" cy="1504080"/>
+          <a:ext cx="3218040" cy="1503720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2820,10 +2813,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>107280</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4170960</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>2094480</xdr:rowOff>
+      <xdr:rowOff>2094120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2837,7 +2830,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="24445440"/>
-          <a:ext cx="4171320" cy="2094480"/>
+          <a:ext cx="4170960" cy="2094120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2858,10 +2851,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>21600</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4085280</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>2647080</xdr:rowOff>
+      <xdr:rowOff>2646720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2875,7 +2868,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="27370440"/>
-          <a:ext cx="4085640" cy="2647080"/>
+          <a:ext cx="4085280" cy="2646720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2896,10 +2889,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>307440</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4371120</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>1761120</xdr:rowOff>
+      <xdr:rowOff>1760760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2913,7 +2906,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="30465360"/>
-          <a:ext cx="4371480" cy="1761120"/>
+          <a:ext cx="4371120" cy="1760760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2934,10 +2927,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>488160</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>4551840</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>2932920</xdr:rowOff>
+      <xdr:rowOff>2932560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2951,7 +2944,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="28354680" y="32654160"/>
-          <a:ext cx="4552200" cy="2932920"/>
+          <a:ext cx="4551840" cy="2932560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3165,7 +3158,7 @@
       <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3330,7 +3323,7 @@
       <c r="D18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3372,7 +3365,7 @@
       <c r="D21" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3400,7 +3393,7 @@
       <c r="D23" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3428,7 +3421,7 @@
       <c r="D25" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3537,7 +3530,7 @@
       <c r="D33" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3579,7 +3572,7 @@
       <c r="D36" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F36" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3649,7 +3642,7 @@
       <c r="D41" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="F41" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3677,7 +3670,7 @@
       <c r="D43" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F43" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3705,7 +3698,7 @@
       <c r="D45" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3922,7 +3915,7 @@
       <c r="D8" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4048,7 +4041,7 @@
       <c r="D17" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4090,7 +4083,7 @@
       <c r="D20" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="F20" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4213,7 +4206,7 @@
       <c r="D29" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4255,7 +4248,7 @@
       <c r="D32" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4434,7 +4427,7 @@
       <c r="D45" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4490,7 +4483,7 @@
       <c r="D49" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F49" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4518,7 +4511,7 @@
       <c r="D51" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4599,7 +4592,7 @@
       <c r="D57" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4655,7 +4648,7 @@
       <c r="D61" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4711,7 +4704,7 @@
       <c r="D65" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="F65" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4781,7 +4774,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="115.37"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="126.51"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="5" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="79.84"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4810,7 +4805,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>364</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -4889,7 +4884,7 @@
       <c r="D8" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4917,7 +4912,7 @@
       <c r="D10" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4987,7 +4982,7 @@
       <c r="D15" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5001,7 +4996,7 @@
       <c r="D16" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5096,7 +5091,7 @@
       <c r="D23" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5124,7 +5119,7 @@
       <c r="D25" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5236,7 +5231,7 @@
       <c r="D33" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="F33" s="2" t="s">
+      <c r="F33" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5317,7 +5312,7 @@
       <c r="D39" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5359,7 +5354,7 @@
       <c r="D42" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F42" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5429,7 +5424,7 @@
       <c r="D47" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="F47" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5471,7 +5466,7 @@
       <c r="D50" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -5538,7 +5533,7 @@
       <c r="D55" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="1" t="s">
         <v>6</v>
       </c>
     </row>
